--- a/chicago/reference/resident-research/T-0462/T-0462_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0462/T-0462_resident_research_working.xlsx
@@ -9741,7 +9741,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>none_recorded (reconstructed)</t>
+          <t>priest (attested)</t>
         </is>
       </c>
       <c r="P75" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0462/T-0462_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0462/T-0462_resident_research_working.xlsx
@@ -1498,7 +1498,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad; isa_public_domain_land_tract_sales</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad; isa_public_domain_land_tract_sales</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>chicago_democrat_1833_1835</t>
+          <t>chicago_democrat_1833_1835; isa_public_domain_land_tract_sales</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9710,7 +9710,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>chicago_democrat_1833_1835</t>
+          <t>chicago_democrat_1833_1835; fergus_chicago_directory_1839; st_cyr_register_ichr_v4</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0462/T-0462_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0462/T-0462_resident_research_working.xlsx
@@ -1994,7 +1994,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad; kinzie_waubun_1856</t>
+          <t>andreas_1884_v1; chicago_antiquities_american_fur_co; chicago_voter_lists_1833_1835_irad; kinzie_waubun_1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0462/T-0462_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0462/T-0462_resident_research_working.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; census_1840_chicago_familysearch_images; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; norris_directory_1844</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_american_1835; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_antiquities_american_fur_co; chicago_voter_lists_1833_1835_irad; kinzie_waubun_1856</t>
+          <t>andreas_1884_v1; chicago_american_1835; chicago_antiquities_american_fur_co; chicago_voter_lists_1833_1835_irad; kinzie_waubun_1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_1843_old_settler_death_notices; st_cyr_register_ichr_v4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; census_1840_chicago_familysearch_images; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; norris_directory_1844</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839; norris_directory_1844</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; baptisthistoryhomepage; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; baptisthistoryhomepage; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0462/T-0462_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0462/T-0462_resident_research_working.xlsx
@@ -2738,7 +2738,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; census_1840_chicago_familysearch_images; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; norris_directory_1844</t>
+          <t>andreas_1884_v1; census_1840_chicago_familysearch_images; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; isa_public_domain_land_tract_sales; norris_directory_1844</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0462/T-0462_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0462/T-0462_resident_research_working.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1843</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; census_1840_chicago_familysearch_images; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1843; norris_directory_1844</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; blackhawk_war_chicago_enrollments_isa; chicago_american_1835; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; norris_directory_1844</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_antiquities_american_fur_co; chicago_voter_lists_1833_1835_irad; kinzie_waubun_1856</t>
+          <t>andreas_1884_v1; chicago_american_1835; chicago_antiquities_american_fur_co; chicago_voter_lists_1833_1835_irad; fergus_1843_old_settler_death_notices; fergus_chicago_directory_1843; kinzie_waubun_1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_1843_old_settler_death_notices; st_cyr_register_ichr_v4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; census_1840_chicago_familysearch_images; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1843; isa_public_domain_land_tract_sales; norris_directory_1844</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839; fergus_chicago_directory_1843; norris_directory_1844</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; baptisthistoryhomepage; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; baptisthistoryhomepage; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1843</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0462/T-0462_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0462/T-0462_resident_research_working.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; census_1840_chicago_familysearch_images; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; norris_directory_1844</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_american_1835; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_antiquities_american_fur_co; chicago_voter_lists_1833_1835_irad; kinzie_waubun_1856</t>
+          <t>andreas_1884_v1; chicago_american_1835; chicago_antiquities_american_fur_co; chicago_voter_lists_1833_1835_irad; kinzie_waubun_1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_1843_old_settler_death_notices; st_cyr_register_ichr_v4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; census_1840_chicago_familysearch_images; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; isa_public_domain_land_tract_sales; norris_directory_1844</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839; norris_directory_1844</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; baptisthistoryhomepage; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; baptisthistoryhomepage; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0462/T-0462_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0462/T-0462_resident_research_working.xlsx
@@ -2738,7 +2738,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; census_1840_chicago_familysearch_images; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; isa_public_domain_land_tract_sales; norris_directory_1844</t>
+          <t>andreas_1884_v1; census_1840_chicago_familysearch_images; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839; isa_public_domain_land_tract_sales; norris_directory_1844</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
